--- a/it_forms/020_software_vulnerability_assessment_survey--it_forms.xlsx
+++ b/it_forms/020_software_vulnerability_assessment_survey--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'software_1'}</t>
+          <t>software_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'software_1'}</t>
+          <t>software 1</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'software_2'}</t>
+          <t>software_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'software_2'}</t>
+          <t>software 2</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'software_3'}</t>
+          <t>software_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'software_3'}</t>
+          <t>software 3</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'software_4'}</t>
+          <t>software_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'software_4'}</t>
+          <t>software 4</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'software_5'}</t>
+          <t>software_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'software_5'}</t>
+          <t>software 5</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'software_6'}</t>
+          <t>software_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'software_6'}</t>
+          <t>software 6</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'software_7'}</t>
+          <t>software_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'software_7'}</t>
+          <t>software 7</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'software_8'}</t>
+          <t>software_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'software_8'}</t>
+          <t>software 8</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'software_9'}</t>
+          <t>software_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'software_9'}</t>
+          <t>software 9</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'software_10'}</t>
+          <t>software_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'software_10'}</t>
+          <t>software 10</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'type_1'}</t>
+          <t>type 1</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'type_2'}</t>
+          <t>type 2</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'type_3'}</t>
+          <t>type 3</t>
         </is>
       </c>
     </row>
